--- a/data/TTN/最新版班表/TTN_TD.xlsx
+++ b/data/TTN/最新版班表/TTN_TD.xlsx
@@ -934,10 +934,10 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
-8:00</t>
+          <t>6:02
+ND0026
+14:13
+8:11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1139,20 +1139,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>8:02
-ND0055
-16:08
-8:06</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>7:22
-ND0047
-15:22
-8:00</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1220,20 +1214,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="W8" s="1" t="inlineStr">
-        <is>
-          <t>4:42
-ND0015
-12:42
-8:00</t>
-        </is>
-      </c>
-      <c r="X8" s="1" t="inlineStr">
-        <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="Y8" s="1" t="inlineStr">
@@ -1856,10 +1844,10 @@
       </c>
       <c r="W11" s="1" t="inlineStr">
         <is>
-          <t>4:00
-STD1
-13:00
-9:00</t>
+          <t>4:42
+ND0015
+12:42
+8:00</t>
         </is>
       </c>
       <c r="X11" s="1" t="inlineStr">
@@ -2383,12 +2371,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>6:07
-ND0028
-15:33
-9:26</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="N14" s="1" t="inlineStr">
@@ -4216,12 +4201,9 @@
 8:51</t>
         </is>
       </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -4643,12 +4625,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-H9
-17:30
-8:00</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MLP</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5920,9 +5899,9 @@
       </c>
       <c r="T31" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
+          <t>6:02
+ND0024
+14:02
 8:00</t>
         </is>
       </c>
@@ -7512,16 +7491,14 @@
 </t>
         </is>
       </c>
-      <c r="L39" s="1" t="inlineStr">
-        <is>
-          <t>
-</t>
-        </is>
-      </c>
-      <c r="M39" s="1" t="inlineStr">
-        <is>
-          <t>
-</t>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>TTN1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>TTN1</t>
         </is>
       </c>
       <c r="N39" s="1" t="inlineStr">
@@ -7912,18 +7889,18 @@
       </c>
       <c r="L41" s="1" t="inlineStr">
         <is>
-          <t>11:30
-STD3
-19:30
+          <t>7:22
+ND0047
+15:22
 8:00</t>
         </is>
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
-          <t>6:57
-ND0088
-14:57
-8:00</t>
+          <t>6:07
+ND0028
+15:33
+9:26</t>
         </is>
       </c>
       <c r="N41" s="1" t="inlineStr">
@@ -8180,9 +8157,9 @@
       </c>
       <c r="T42" s="1" t="inlineStr">
         <is>
-          <t>6:02
-ND0024
-14:02
+          <t>8:30
+LUT
+17:30
 8:00</t>
         </is>
       </c>
@@ -8760,9 +8737,9 @@
       </c>
       <c r="M45" s="1" t="inlineStr">
         <is>
-          <t>6:00
-STD2
-14:00
+          <t>6:57
+ND0088
+14:57
 8:00</t>
         </is>
       </c>
@@ -9578,20 +9555,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>9:32
-ND0095
-17:33
-8:01</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>11:17
-ND0073
-19:17
-8:00</t>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>STD</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NHS1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -11682,10 +11653,10 @@
       </c>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>6:02
-ND0026
-14:13
-8:11</t>
+          <t>8:02
+ND0055
+16:08
+8:06</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
